--- a/data/mini-example-resilience/Power_Network.xlsx
+++ b/data/mini-example-resilience/Power_Network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F25EE77-FBDA-45F8-A62E-7CDF1687D8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BA84FA-E1C0-4CFD-A00C-B6184D75332E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="78">
   <si>
     <t>Power - Network</t>
   </si>
@@ -336,6 +336,18 @@
   </si>
   <si>
     <t>[dataSource]</t>
+  </si>
+  <si>
+    <t>Node_1</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>Node_feedin</t>
+  </si>
+  <si>
+    <t>TP</t>
   </si>
 </sst>
 </file>
@@ -1121,19 +1133,41 @@
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="15"/>
+      <c r="C8" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="13">
+        <v>1</v>
+      </c>
+      <c r="G8" s="13">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13">
+        <v>1</v>
+      </c>
+      <c r="I8" s="13">
+        <v>1</v>
+      </c>
+      <c r="J8" s="13">
+        <v>1</v>
+      </c>
+      <c r="K8" s="14">
+        <v>20</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0</v>
+      </c>
       <c r="M8" s="16"/>
       <c r="N8" s="16"/>
-      <c r="O8" s="17"/>
+      <c r="O8" s="17" t="s">
+        <v>77</v>
+      </c>
       <c r="P8" s="15"/>
       <c r="Q8" s="15"/>
       <c r="R8" s="17"/>
